--- a/CPRD Raw Analysis/Results/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>496.55</v>
+        <v>727.9</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8450.17</v>
+        <v>16052.42</v>
       </c>
       <c r="F2">
-        <v>465.23</v>
+        <v>693.0599999999999</v>
       </c>
       <c r="G2">
-        <v>185</v>
+        <v>261.16</v>
       </c>
       <c r="H2">
-        <v>373.28</v>
+        <v>539.78</v>
       </c>
       <c r="I2">
-        <v>665.21</v>
+        <v>975.89</v>
       </c>
       <c r="J2">
         <v>23106</v>
       </c>
       <c r="K2">
-        <v>11473373.07</v>
+        <v>16818921.2</v>
       </c>
       <c r="L2">
-        <v>496.55</v>
+        <v>727.9</v>
       </c>
       <c r="M2">
-        <v>3.06</v>
+        <v>4.56</v>
       </c>
       <c r="N2">
-        <v>490.55</v>
+        <v>718.97</v>
       </c>
       <c r="O2">
-        <v>502.55</v>
+        <v>736.84</v>
       </c>
     </row>
     <row r="3">
@@ -490,337 +490,141 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>421.95</v>
+        <v>622.92</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5759.32</v>
+        <v>9340</v>
       </c>
       <c r="F3">
-        <v>438.48</v>
+        <v>652.92</v>
       </c>
       <c r="G3">
-        <v>118.64</v>
+        <v>174.8</v>
       </c>
       <c r="H3">
-        <v>303.46</v>
+        <v>445.69</v>
       </c>
       <c r="I3">
-        <v>579.88</v>
+        <v>851.8200000000001</v>
       </c>
       <c r="J3">
         <v>14300</v>
       </c>
       <c r="K3">
-        <v>6033822.19</v>
+        <v>8907705.699999999</v>
       </c>
       <c r="L3">
-        <v>261.14</v>
+        <v>385.51</v>
       </c>
       <c r="M3">
-        <v>3.67</v>
+        <v>5.46</v>
       </c>
       <c r="N3">
-        <v>414.76</v>
+        <v>612.21</v>
       </c>
       <c r="O3">
-        <v>429.13</v>
+        <v>633.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>476.31</v>
+        <v>747.98</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8424.719999999999</v>
+        <v>16052.42</v>
       </c>
       <c r="F4">
-        <v>454.02</v>
+        <v>692.04</v>
       </c>
       <c r="G4">
-        <v>169.89</v>
+        <v>284.32</v>
       </c>
       <c r="H4">
-        <v>355.2</v>
+        <v>560.42</v>
       </c>
       <c r="I4">
-        <v>639.48</v>
+        <v>992.36</v>
       </c>
       <c r="J4">
-        <v>23106</v>
+        <v>22478</v>
       </c>
       <c r="K4">
-        <v>11005605.22</v>
+        <v>16813002.84</v>
       </c>
       <c r="L4">
-        <v>476.31</v>
+        <v>747.98</v>
       </c>
       <c r="M4">
-        <v>2.99</v>
+        <v>4.62</v>
       </c>
       <c r="N4">
-        <v>470.45</v>
+        <v>738.9299999999999</v>
       </c>
       <c r="O4">
-        <v>482.16</v>
+        <v>757.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>407.98</v>
+        <v>627.87</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5468</v>
+        <v>9340</v>
       </c>
       <c r="F5">
-        <v>427.47</v>
+        <v>653.14</v>
       </c>
       <c r="G5">
-        <v>111</v>
+        <v>180.5</v>
       </c>
       <c r="H5">
-        <v>296</v>
+        <v>449.61</v>
       </c>
       <c r="I5">
-        <v>560.67</v>
+        <v>856.25</v>
       </c>
       <c r="J5">
-        <v>14300</v>
+        <v>14187</v>
       </c>
       <c r="K5">
-        <v>5834177.48</v>
+        <v>8907582.939999999</v>
       </c>
       <c r="L5">
-        <v>252.5</v>
+        <v>396.28</v>
       </c>
       <c r="M5">
-        <v>3.57</v>
+        <v>5.48</v>
       </c>
       <c r="N5">
-        <v>400.98</v>
+        <v>617.12</v>
       </c>
       <c r="O5">
-        <v>414.99</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>510.51</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>8450.17</v>
-      </c>
-      <c r="F6">
-        <v>464.3</v>
-      </c>
-      <c r="G6">
-        <v>196.81</v>
-      </c>
-      <c r="H6">
-        <v>384.35</v>
-      </c>
-      <c r="I6">
-        <v>677.01</v>
-      </c>
-      <c r="J6">
-        <v>22466</v>
-      </c>
-      <c r="K6">
-        <v>11469038.49</v>
-      </c>
-      <c r="L6">
-        <v>510.51</v>
-      </c>
-      <c r="M6">
-        <v>3.1</v>
-      </c>
-      <c r="N6">
-        <v>504.43</v>
-      </c>
-      <c r="O6">
-        <v>516.58</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>425.33</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>5759.32</v>
-      </c>
-      <c r="F7">
-        <v>438.61</v>
-      </c>
-      <c r="G7">
-        <v>121.37</v>
-      </c>
-      <c r="H7">
-        <v>305.84</v>
-      </c>
-      <c r="I7">
-        <v>582.39</v>
-      </c>
-      <c r="J7">
-        <v>14186</v>
-      </c>
-      <c r="K7">
-        <v>6033738.88</v>
-      </c>
-      <c r="L7">
-        <v>268.57</v>
-      </c>
-      <c r="M7">
-        <v>3.68</v>
-      </c>
-      <c r="N7">
-        <v>418.11</v>
-      </c>
-      <c r="O7">
-        <v>432.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>489.88</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>8424.719999999999</v>
-      </c>
-      <c r="F8">
-        <v>453.17</v>
-      </c>
-      <c r="G8">
-        <v>185</v>
-      </c>
-      <c r="H8">
-        <v>370</v>
-      </c>
-      <c r="I8">
-        <v>652.41</v>
-      </c>
-      <c r="J8">
-        <v>22466</v>
-      </c>
-      <c r="K8">
-        <v>11005605.22</v>
-      </c>
-      <c r="L8">
-        <v>489.88</v>
-      </c>
-      <c r="M8">
-        <v>3.02</v>
-      </c>
-      <c r="N8">
-        <v>483.95</v>
-      </c>
-      <c r="O8">
-        <v>495.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>411.26</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>5468</v>
-      </c>
-      <c r="F9">
-        <v>427.61</v>
-      </c>
-      <c r="G9">
-        <v>112.9</v>
-      </c>
-      <c r="H9">
-        <v>296</v>
-      </c>
-      <c r="I9">
-        <v>563.2</v>
-      </c>
-      <c r="J9">
-        <v>14186</v>
-      </c>
-      <c r="K9">
-        <v>5834177.48</v>
-      </c>
-      <c r="L9">
-        <v>259.69</v>
-      </c>
-      <c r="M9">
-        <v>3.59</v>
-      </c>
-      <c r="N9">
-        <v>404.23</v>
-      </c>
-      <c r="O9">
-        <v>418.3</v>
+        <v>638.62</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>727.9</v>
+        <v>934.52</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16052.42</v>
+        <v>39234.21</v>
       </c>
       <c r="F2">
-        <v>693.0599999999999</v>
+        <v>1244.7</v>
       </c>
       <c r="G2">
-        <v>261.16</v>
+        <v>329.01</v>
       </c>
       <c r="H2">
-        <v>539.78</v>
+        <v>664.61</v>
       </c>
       <c r="I2">
-        <v>975.89</v>
+        <v>1196.44</v>
       </c>
       <c r="J2">
         <v>23106</v>
       </c>
       <c r="K2">
-        <v>16818921.2</v>
+        <v>21593119.8</v>
       </c>
       <c r="L2">
-        <v>727.9</v>
+        <v>934.52</v>
       </c>
       <c r="M2">
-        <v>4.56</v>
+        <v>8.19</v>
       </c>
       <c r="N2">
-        <v>718.97</v>
+        <v>918.47</v>
       </c>
       <c r="O2">
-        <v>736.84</v>
+        <v>950.5700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -490,43 +490,43 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>622.92</v>
+        <v>431.12</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9340</v>
+        <v>40257.84</v>
       </c>
       <c r="F3">
-        <v>652.92</v>
+        <v>925.28</v>
       </c>
       <c r="G3">
-        <v>174.8</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>445.69</v>
+        <v>164.32</v>
       </c>
       <c r="I3">
-        <v>851.8200000000001</v>
+        <v>549.24</v>
       </c>
       <c r="J3">
         <v>14300</v>
       </c>
       <c r="K3">
-        <v>8907705.699999999</v>
+        <v>6164987.9</v>
       </c>
       <c r="L3">
-        <v>385.51</v>
+        <v>266.81</v>
       </c>
       <c r="M3">
-        <v>5.46</v>
+        <v>7.74</v>
       </c>
       <c r="N3">
-        <v>612.21</v>
+        <v>415.95</v>
       </c>
       <c r="O3">
-        <v>633.62</v>
+        <v>446.28</v>
       </c>
     </row>
     <row r="4">
@@ -539,43 +539,43 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>747.98</v>
+        <v>1043.6</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>16052.42</v>
+        <v>39234.21</v>
       </c>
       <c r="F4">
-        <v>692.04</v>
+        <v>1271.32</v>
       </c>
       <c r="G4">
-        <v>284.32</v>
+        <v>378.34</v>
       </c>
       <c r="H4">
-        <v>560.42</v>
+        <v>732.89</v>
       </c>
       <c r="I4">
-        <v>992.36</v>
+        <v>1292.49</v>
       </c>
       <c r="J4">
-        <v>22478</v>
+        <v>20691</v>
       </c>
       <c r="K4">
-        <v>16813002.84</v>
+        <v>21593119.8</v>
       </c>
       <c r="L4">
-        <v>747.98</v>
+        <v>1043.6</v>
       </c>
       <c r="M4">
-        <v>4.62</v>
+        <v>8.84</v>
       </c>
       <c r="N4">
-        <v>738.9299999999999</v>
+        <v>1026.28</v>
       </c>
       <c r="O4">
-        <v>757.02</v>
+        <v>1060.92</v>
       </c>
     </row>
     <row r="5">
@@ -588,43 +588,43 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>627.87</v>
+        <v>461.45</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9340</v>
+        <v>40257.84</v>
       </c>
       <c r="F5">
-        <v>653.14</v>
+        <v>949.9400000000001</v>
       </c>
       <c r="G5">
-        <v>180.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>449.61</v>
+        <v>179.56</v>
       </c>
       <c r="I5">
-        <v>856.25</v>
+        <v>595.37</v>
       </c>
       <c r="J5">
-        <v>14187</v>
+        <v>13360</v>
       </c>
       <c r="K5">
-        <v>8907582.939999999</v>
+        <v>6164987.9</v>
       </c>
       <c r="L5">
-        <v>396.28</v>
+        <v>297.96</v>
       </c>
       <c r="M5">
-        <v>5.48</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N5">
-        <v>617.12</v>
+        <v>445.34</v>
       </c>
       <c r="O5">
-        <v>638.62</v>
+        <v>477.56</v>
       </c>
     </row>
   </sheetData>
